--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -526,6 +526,9 @@
       <c r="A11" t="str">
         <v>5</v>
       </c>
+      <c r="C11" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -529,10 +529,99 @@
       <c r="C11" t="str">
         <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>6</v>
+      </c>
+      <c r="C13" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F13" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F14" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F15" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>7</v>
+      </c>
+      <c r="C16" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F17" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F18" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>8</v>
+      </c>
+      <c r="C20" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +676,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03040203025154020400</v>
+        <v>0304020302515402040102630301520530680</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -618,6 +618,9 @@
       <c r="C21" t="str">
         <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F21" t="str">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -676,7 +679,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0304020302515402040102630301520530680</v>
+        <v>0304020302515402040102630301520530682</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -619,7 +619,7 @@
         <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F21" t="str">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -679,7 +679,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0304020302515402040102630301520530682</v>
+        <v>03040203025154020401026303015205306820</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -622,9 +622,101 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F23" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>9</v>
+      </c>
+      <c r="C24" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>10</v>
+      </c>
+      <c r="C25" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>261_单头蓝莓_Blueberry_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>11</v>
+      </c>
+      <c r="C28" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>12</v>
+      </c>
+      <c r="C30" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -679,7 +771,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03040203025154020401026303015205306820</v>
+        <v>030402030251540204010263030152053068201030378122420222810</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -714,9 +714,98 @@
         <v>10</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>13</v>
+      </c>
+      <c r="C32" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v/>
+      </c>
+      <c r="C33" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>14</v>
+      </c>
+      <c r="C35" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>15</v>
+      </c>
+      <c r="C40" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -771,7 +860,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030402030251540204010263030152053068201030378122420222810</v>
+        <v>03040203025154020401026303015205306820103037812242022281018714287166310</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -802,10 +802,105 @@
       <c r="C41" t="str">
         <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>16</v>
+      </c>
+      <c r="C43" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>17</v>
+      </c>
+      <c r="C45" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>18</v>
+      </c>
+      <c r="C48" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>19</v>
+      </c>
+      <c r="C50" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -860,7 +955,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03040203025154020401026303015205306820103037812242022281018714287166310</v>
+        <v>0304020302515402040102630301520530682010303781224202228101871428716631202083615329192710</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -897,6 +897,9 @@
       <c r="C51" t="str">
         <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F51" t="str">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -955,7 +958,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0304020302515402040102630301520530682010303781224202228101871428716631202083615329192710</v>
+        <v>03040203025154020401026303015205306820103037812242022281018714287166312020836153291927134</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -901,9 +901,95 @@
         <v>34</v>
       </c>
     </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>20</v>
+      </c>
+      <c r="C53" t="str">
+        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>21</v>
+      </c>
+      <c r="C56" t="str">
+        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>22</v>
+      </c>
+      <c r="C60" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>c</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -958,7 +1044,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03040203025154020401026303015205306820103037812242022281018714287166312020836153291927134</v>
+        <v>030402030251540204010263030152053068201030378122420222810187142871663120208361532919271345181612208330100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -984,7 +984,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>c</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -986,6 +986,12 @@
       <c r="A61" t="str">
         <v/>
       </c>
+      <c r="C61" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F61" t="str">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1044,7 +1050,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030402030251540204010263030152053068201030378122420222810187142871663120208361532919271345181612208330100</v>
+        <v>0304020302515402040102630301520530682010303781224202228101871428716631202083615329192713451816122083301037</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -993,9 +993,95 @@
         <v>37</v>
       </c>
     </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F62" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>23</v>
+      </c>
+      <c r="C63" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F63" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F65" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F66" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>24</v>
+      </c>
+      <c r="C67" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F67" t="str">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F68" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F69" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>25</v>
+      </c>
+      <c r="C70" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F70" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1050,7 +1136,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0304020302515402040102630301520530682010303781224202228101871428716631202083615329192713451816122083301037</v>
+        <v>03040203025154020401026303015205306820103037812242022281018714287166312020836153291927134518161220833010371018303437102250</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1078,10 +1078,194 @@
       <c r="C71" t="str">
         <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F71" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F72" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>26</v>
+      </c>
+      <c r="C73" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F73" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F74" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>27</v>
+      </c>
+      <c r="C75" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F75" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F76" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F77" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>28</v>
+      </c>
+      <c r="C78" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F78" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F79" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>29</v>
+      </c>
+      <c r="C80" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F81" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F82" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F83" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>30</v>
+      </c>
+      <c r="C84" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F84" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F85" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>31</v>
+      </c>
+      <c r="C86" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F86" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F87" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>32</v>
+      </c>
+      <c r="C88" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F88" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F89" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F90" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L91"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1136,7 +1320,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03040203025154020401026303015205306820103037812242022281018714287166312020836153291927134518161220833010371018303437102250</v>
+        <v>030402030251540204010263030152053068201030378122420222810187142871663120208361532919271345181612208330103710183034371022532024826242684112341030308146120</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -1262,6 +1262,9 @@
       <c r="C91" t="str">
         <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F91" t="str">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1320,7 +1323,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030402030251540204010263030152053068201030378122420222810187142871663120208361532919271345181612208330103710183034371022532024826242684112341030308146120</v>
+        <v>030402030251540204010263030152053068201030378122420222810187142871663120208361532919271345181612208330103710183034371022532024826242684112341030308146128</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1266,9 +1266,98 @@
         <v>8</v>
       </c>
     </row>
+    <row r="92">
+      <c r="C92" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F92" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>33</v>
+      </c>
+      <c r="C93" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F93" t="str">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>34</v>
+      </c>
+      <c r="C94" t="str">
+        <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F94" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F95" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F96" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>35</v>
+      </c>
+      <c r="C97" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F97" t="str">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F98" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>36</v>
+      </c>
+      <c r="C99" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F99" t="str">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="C100" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F100" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1323,7 +1412,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030402030251540204010263030152053068201030378122420222810187142871663120208361532919271345181612208330103710183034371022532024826242684112341030308146128</v>
+        <v>030402030251540204010263030152053068201030378122420222810187142871663120208361532919271345181612208330103710183034371022532024826242684112341030308146128353242223263950</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-14.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-14.xlsx
@@ -1354,6 +1354,9 @@
       <c r="A101" t="str">
         <v>37</v>
       </c>
+      <c r="C101" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
